--- a/01_Thermal/B_results/four_annular_var_analysis.xlsx
+++ b/01_Thermal/B_results/four_annular_var_analysis.xlsx
@@ -498,28 +498,28 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>56.79735092189993</v>
+        <v>56.71357964576603</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3720642780397</v>
+        <v>0.363795573918716</v>
       </c>
       <c r="F2" t="n">
-        <v>589.788211868633</v>
+        <v>248.0110134387576</v>
       </c>
       <c r="G2" t="n">
-        <v>4260.495759386248</v>
+        <v>1873.942000315514</v>
       </c>
       <c r="H2" t="n">
-        <v>9.198676639139755</v>
+        <v>9.344428292875257</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2872541201410848</v>
+        <v>0.2862253642054461</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1630825379591276</v>
+        <v>0.1624416018005918</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07666690673329438</v>
+        <v>0.07541454071275144</v>
       </c>
     </row>
     <row r="3">
@@ -535,28 +535,28 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>63.01301487487336</v>
+        <v>61.60261823503038</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4728156773090082</v>
+        <v>0.3296691121174426</v>
       </c>
       <c r="F3" t="n">
-        <v>1232.431564057195</v>
+        <v>240.0699294872541</v>
       </c>
       <c r="G3" t="n">
-        <v>5512.886817461288</v>
+        <v>2208.926411826067</v>
       </c>
       <c r="H3" t="n">
-        <v>3.715327307204904</v>
+        <v>3.753778586301195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2979115499947765</v>
+        <v>0.3254493477119523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3336350733970883</v>
+        <v>0.2699657371945505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05268698501985411</v>
+        <v>0.06511331986030697</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>62.95381833616823</v>
+        <v>62.87010011110504</v>
       </c>
       <c r="E4" t="n">
-        <v>0.421187308026266</v>
+        <v>0.4540993274654768</v>
       </c>
       <c r="F4" t="n">
-        <v>668.2069653101361</v>
+        <v>425.6908926119587</v>
       </c>
       <c r="G4" t="n">
-        <v>3766.694924158668</v>
+        <v>2064.394253198892</v>
       </c>
       <c r="H4" t="n">
-        <v>2.384872482823412</v>
+        <v>2.366057855013973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3814656957315016</v>
+        <v>0.3786960083939125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3382143252434714</v>
+        <v>0.3215274513974399</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05151551083768402</v>
+        <v>0.06496209792479402</v>
       </c>
     </row>
     <row r="5">
@@ -609,28 +609,28 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>64.46099842848371</v>
+        <v>64.20627807265903</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4172886930364203</v>
+        <v>0.3489750028153365</v>
       </c>
       <c r="F5" t="n">
-        <v>2983.795179458137</v>
+        <v>956.6244017328364</v>
       </c>
       <c r="G5" t="n">
-        <v>17135.46024586532</v>
+        <v>7855.11985311939</v>
       </c>
       <c r="H5" t="n">
-        <v>2.645704906928875</v>
+        <v>2.654855531540862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5057845137098679</v>
+        <v>0.5053821075001481</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2463982842020314</v>
+        <v>0.2537781750380912</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08951081109829767</v>
+        <v>0.08355179200659028</v>
       </c>
     </row>
     <row r="6">
@@ -646,28 +646,28 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>63.99976298257183</v>
+        <v>64.0276999642971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3957522783486028</v>
+        <v>0.4086158346670196</v>
       </c>
       <c r="F6" t="n">
-        <v>1119.951452048171</v>
+        <v>925.6980951297344</v>
       </c>
       <c r="G6" t="n">
-        <v>7150.76242849565</v>
+        <v>5544.201235342096</v>
       </c>
       <c r="H6" t="n">
-        <v>1.74401855732209</v>
+        <v>1.730642286748588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3366238241511047</v>
+        <v>0.3954343663143721</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6331909734884641</v>
+        <v>0.5177991551009251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02911937593082523</v>
+        <v>0.05181714406754422</v>
       </c>
     </row>
     <row r="7">
@@ -683,28 +683,28 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>48.7906205976311</v>
+        <v>48.78670145864197</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3434186097093205</v>
+        <v>0.3199004871395457</v>
       </c>
       <c r="F7" t="n">
-        <v>802.7471550451298</v>
+        <v>648.4363258037952</v>
       </c>
       <c r="G7" t="n">
-        <v>6806.614016268456</v>
+        <v>6336.326293623866</v>
       </c>
       <c r="H7" t="n">
-        <v>1.47954900492459</v>
+        <v>1.471807945021149</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2428496067818824</v>
+        <v>0.238180424821621</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6782663030137023</v>
+        <v>0.703941181395799</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03270659404401784</v>
+        <v>0.02880713942981006</v>
       </c>
     </row>
     <row r="8">
@@ -720,28 +720,28 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>56.2459818289534</v>
+        <v>56.22206589660374</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3540675852009528</v>
+        <v>0.3784356575611049</v>
       </c>
       <c r="F8" t="n">
-        <v>639.0716073239238</v>
+        <v>779.6236671701821</v>
       </c>
       <c r="G8" t="n">
-        <v>5097.734174531417</v>
+        <v>5443.784362382623</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9002915747575302</v>
+        <v>0.8959492238099107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4965060020743002</v>
+        <v>0.4832352667623759</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7393579215291157</v>
+        <v>0.7557469533045313</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02823476797607735</v>
+        <v>0.02950725840111155</v>
       </c>
     </row>
     <row r="9">
@@ -755,16 +755,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>416.2615479705816</v>
+        <v>414.4290433841033</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4019830035184797</v>
+        <v>0.3672083962997775</v>
       </c>
       <c r="F9" t="n">
-        <v>8035.992135111326</v>
+        <v>4224.154325374519</v>
       </c>
       <c r="G9" t="n">
-        <v>49730.64836616704</v>
+        <v>31326.69440980845</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
